--- a/output_phyto/phyto_Intermediate_bolton_2016.xlsx
+++ b/output_phyto/phyto_Intermediate_bolton_2016.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t>NA</t>
   </si>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1038/ncomms10284</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_bolton_2016.xlsx</t>
+    <t xml:space="preserve">phytoplankton_bolton_2016_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,28 +1475,34 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
+    <t xml:space="preserve">published temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values for site 999 from Badger et al. (2013a).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2aq and pCO2 and their uncertainties represent the averages of the maximum and minimum values based on maximum and minimum b values, as well as max and min Ep values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Bolton_2016_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">assumed based on projection of Plio/Pleistocene temperatures at ODP 999 from Seki et al. (2010) and trend at ODP Site 1010 and 1241 in Miocene (LaRiviere et al., 2012; Seki et al., 2012). See Bolton and Stoll (2013; Nature) Figure S5 for details. Value here is the "max SST" from that figure, which is much more reasonable than the "min" temperature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2aq and pCO2 and their uncertainties represent the averages of the maximum and minimum values based on maximum and minimum b values, as well as max and min Ep values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Bolton_2016_7</t>
   </si>
   <si>
     <t xml:space="preserve">Used as foraminifera d13C value for preceding sample because no foraminifera were found in sample algae_Bolton_2016_6</t>
@@ -1525,7 +1531,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1591,12 +1597,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1710,7 +1710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1809,7 +1809,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2535,7 +2534,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2553,8 +2552,8 @@
       <c r="H5" t="n">
         <v>4.0088701171875</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.03</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2571,8 +2570,8 @@
       <c r="N5" t="n">
         <v>-24.285</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2583,8 +2582,8 @@
       <c r="R5" s="11" t="n">
         <v>29.8</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3.6</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2595,20 +2594,20 @@
       <c r="V5" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W5" t="e">
-        <v>#N/A</v>
+      <c r="W5" t="n">
+        <v>0.2</v>
       </c>
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>278</v>
       </c>
       <c r="AB5" t="n">
         <v>3.525</v>
@@ -2622,8 +2621,8 @@
       <c r="AE5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AF5" t="n">
+        <v>1.82130414294933</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2635,17 +2634,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2663,8 +2662,8 @@
       <c r="H6" t="n">
         <v>5.0025537109375</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.04</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2681,8 +2680,8 @@
       <c r="N6" t="n">
         <v>-24.0315</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2693,8 +2692,8 @@
       <c r="R6" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3.6</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2705,20 +2704,20 @@
       <c r="V6" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W6" t="e">
-        <v>#N/A</v>
+      <c r="W6" t="n">
+        <v>0.2</v>
       </c>
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>278</v>
       </c>
       <c r="AB6" t="n">
         <v>4.625</v>
@@ -2732,8 +2731,8 @@
       <c r="AE6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AF6" t="n">
+        <v>2.30448885614815</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2745,17 +2744,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2773,8 +2772,8 @@
       <c r="H7" t="n">
         <v>6.00348138809204</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.0317511878070742</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2791,8 +2790,8 @@
       <c r="N7" t="n">
         <v>-25.1603333333333</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2803,8 +2802,8 @@
       <c r="R7" s="11" t="n">
         <v>30.24951171875</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3.6</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2815,20 +2814,20 @@
       <c r="V7" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W7" t="e">
-        <v>#N/A</v>
+      <c r="W7" t="n">
+        <v>0.2</v>
       </c>
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>278</v>
       </c>
       <c r="AB7" t="n">
         <v>4.45</v>
@@ -2842,8 +2841,8 @@
       <c r="AE7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AF7" t="n">
+        <v>2.22761856086652</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2855,17 +2854,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2883,8 +2882,8 @@
       <c r="H8" t="n">
         <v>7.00128412246704</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.0367346232191583</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2901,8 +2900,8 @@
       <c r="N8" t="n">
         <v>-24.8803333333333</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2913,8 +2912,8 @@
       <c r="R8" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3.6</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2925,20 +2924,20 @@
       <c r="V8" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W8" t="e">
-        <v>#N/A</v>
+      <c r="W8" t="n">
+        <v>0.2</v>
       </c>
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>278</v>
       </c>
       <c r="AB8" t="n">
         <v>2.725</v>
@@ -2952,8 +2951,8 @@
       <c r="AE8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AF8" t="n">
+        <v>1.46989707880473</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -2965,17 +2964,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -2993,8 +2992,8 @@
       <c r="H9" t="n">
         <v>8.00035667419434</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.0416875504987161</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3011,8 +3010,8 @@
       <c r="N9" t="n">
         <v>-22.3833333333333</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3023,8 +3022,8 @@
       <c r="R9" s="11" t="n">
         <v>31.3</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3.6</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3035,20 +3034,20 @@
       <c r="V9" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W9" t="e">
-        <v>#N/A</v>
+      <c r="W9" t="n">
+        <v>0.2</v>
       </c>
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>278</v>
       </c>
       <c r="AB9" t="n">
         <v>3.875</v>
@@ -3062,8 +3061,8 @@
       <c r="AE9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AF9" t="n">
+        <v>1.97504473351259</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3075,17 +3074,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3103,8 +3102,8 @@
       <c r="H10" t="n">
         <v>9.30813598632812</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.0481231140667412</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3121,8 +3120,8 @@
       <c r="N10" t="n">
         <v>-23.556</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3133,8 +3132,8 @@
       <c r="R10" s="11" t="n">
         <v>31.5</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3.6</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3145,20 +3144,20 @@
       <c r="V10" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W10" t="e">
-        <v>#N/A</v>
+      <c r="W10" t="n">
+        <v>0.2</v>
       </c>
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>278</v>
       </c>
       <c r="AB10" t="n">
         <v>2.06</v>
@@ -3172,8 +3171,8 @@
       <c r="AE10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AF10" t="n">
+        <v>1.17778995673453</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3185,17 +3184,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3213,8 +3212,8 @@
       <c r="H11" t="n">
         <v>9.3183622360229</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.0481732437538689</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3253,22 +3252,22 @@
         <v>#N/A</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="W11" t="e">
-        <v>#N/A</v>
+        <v>286</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2</v>
       </c>
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>278</v>
       </c>
       <c r="AB11" t="e">
         <v>#N/A</v>
@@ -3295,17 +3294,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3323,8 +3322,8 @@
       <c r="H12" t="n">
         <v>10.3301115036011</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.0531193145444271</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3341,8 +3340,8 @@
       <c r="N12" t="n">
         <v>-22.2593333333333</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3353,8 +3352,8 @@
       <c r="R12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3.6</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3365,20 +3364,20 @@
       <c r="V12" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W12" t="e">
-        <v>#N/A</v>
+      <c r="W12" t="n">
+        <v>0.2</v>
       </c>
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>278</v>
       </c>
       <c r="AB12" t="n">
         <v>3.825</v>
@@ -3392,8 +3391,8 @@
       <c r="AE12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AF12" t="n">
+        <v>1.95308179200355</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3405,17 +3404,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3433,8 +3432,8 @@
       <c r="H13" t="n">
         <v>11.2004766464233</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.0573540573537228</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3451,8 +3450,8 @@
       <c r="N13" t="n">
         <v>-22.8053333333333</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3463,8 +3462,8 @@
       <c r="R13" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3.6</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3475,20 +3474,20 @@
       <c r="V13" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W13" t="e">
-        <v>#N/A</v>
+      <c r="W13" t="n">
+        <v>0.2</v>
       </c>
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>278</v>
       </c>
       <c r="AB13" t="n">
         <v>3.95</v>
@@ -3502,8 +3501,8 @@
       <c r="AE13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AF13" t="n">
+        <v>2.00798914577615</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3515,17 +3514,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3543,8 +3542,8 @@
       <c r="H14" t="n">
         <v>12.4634809494019</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.0634692443927513</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3561,8 +3560,8 @@
       <c r="N14" t="n">
         <v>-23.8613333333333</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3573,8 +3572,8 @@
       <c r="R14" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3.6</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3585,20 +3584,20 @@
       <c r="V14" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W14" t="e">
-        <v>#N/A</v>
+      <c r="W14" t="n">
+        <v>0.2</v>
       </c>
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>278</v>
       </c>
       <c r="AB14" t="n">
         <v>3.875</v>
@@ -3612,8 +3611,8 @@
       <c r="AE14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AF14" t="n">
+        <v>1.97504473351259</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3625,17 +3624,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3653,8 +3652,8 @@
       <c r="H15" t="n">
         <v>13.1006994247437</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.0665421334150235</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3671,8 +3670,8 @@
       <c r="N15" t="n">
         <v>-23.0403333333333</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3683,8 +3682,8 @@
       <c r="R15" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3.6</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3695,20 +3694,20 @@
       <c r="V15" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W15" t="e">
-        <v>#N/A</v>
+      <c r="W15" t="n">
+        <v>0.2</v>
       </c>
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>278</v>
       </c>
       <c r="AB15" t="n">
         <v>3.56</v>
@@ -3722,8 +3721,8 @@
       <c r="AE15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AF15" t="n">
+        <v>1.83667820200565</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3735,17 +3734,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3763,8 +3762,8 @@
       <c r="H16" t="n">
         <v>14.3584442138672</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.0725850725082416</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3781,8 +3780,8 @@
       <c r="N16" t="n">
         <v>-24.4856666666667</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3793,8 +3792,8 @@
       <c r="R16" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3.6</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3805,20 +3804,20 @@
       <c r="V16" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W16" t="e">
-        <v>#N/A</v>
+      <c r="W16" t="n">
+        <v>0.2</v>
       </c>
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>278</v>
       </c>
       <c r="AB16" t="n">
         <v>2.075</v>
@@ -3832,8 +3831,8 @@
       <c r="AE16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AF16" t="n">
+        <v>1.18437883918724</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3845,17 +3844,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3873,8 +3872,8 @@
       <c r="H17" t="n">
         <v>15.7561550140381</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.0792684588358887</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3891,8 +3890,8 @@
       <c r="N17" t="n">
         <v>-25.1793333333333</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3903,8 +3902,8 @@
       <c r="R17" s="11" t="n">
         <v>32.7</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3.6</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -3915,20 +3914,20 @@
       <c r="V17" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W17" t="e">
-        <v>#N/A</v>
+      <c r="W17" t="n">
+        <v>0.2</v>
       </c>
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>278</v>
       </c>
       <c r="AB17" t="n">
         <v>2.975</v>
@@ -3942,8 +3941,8 @@
       <c r="AE17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AF17" t="n">
+        <v>1.57971178634992</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -3955,7 +3954,7 @@
         <v>#N/A</v>
       </c>
       <c r="AJ17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -4320,21 +4319,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
